--- a/data/trans_dic/P32E$calle_2023-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P32E$calle_2023-Edad-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, al menos, realiza el atracón de alcohol en la calle</t>
+          <t>Población que, al menos, realiza el atracón de alcohol en la calle (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -577,12 +577,12 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>11,49; 73,41</t>
+          <t>12,85; 74,23</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>25,77; 66,38</t>
+          <t>26,44; 66,47</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4,1; 38,74</t>
+          <t>3,81; 36,69</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 40,9</t>
+          <t>0,0; 54,45</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3,22; 28,93</t>
+          <t>3,52; 31,49</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>7,56; 40,42</t>
+          <t>7,43; 39,5</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 20,75</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6,38; 35,46</t>
+          <t>6,19; 32,58</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>6,89; 36,28</t>
+          <t>6,9; 36,14</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 40,45</t>
+          <t>0,0; 37,57</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5,95; 33,5</t>
+          <t>6,86; 30,49</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0; 6,81</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 46,27</t>
+          <t>0,0; 44,28</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,11</t>
+          <t>0,0; 11,09</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 36,57</t>
+          <t>0,0; 33,01</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 62,75</t>
+          <t>0,0; 63,17</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3,14; 29,99</t>
+          <t>3,29; 31,18</t>
         </is>
       </c>
     </row>
@@ -872,7 +872,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0; 20,75</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -882,7 +882,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 41,82</t>
+          <t>0,0; 43,54</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>12,83; 28,73</t>
+          <t>12,26; 28,28</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>8,39; 33,8</t>
+          <t>7,9; 34,12</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>12,9; 25,32</t>
+          <t>13,28; 25,86</t>
         </is>
       </c>
     </row>
@@ -978,7 +978,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, al menos, realiza el atracón de alcohol en la calle</t>
+          <t>Población que, al menos, realiza el atracón de alcohol en la calle (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1088,12 +1088,12 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1763; 11269</t>
+          <t>1973; 11396</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>10562; 27213</t>
+          <t>10838; 27251</t>
         </is>
       </c>
     </row>
@@ -1156,17 +1156,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>942; 8897</t>
+          <t>876; 8426</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 5538</t>
+          <t>0; 7373</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1174; 10561</t>
+          <t>1286; 11494</t>
         </is>
       </c>
     </row>
@@ -1229,17 +1229,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>2030; 10856</t>
+          <t>1995; 10609</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 1132</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2062; 11455</t>
+          <t>1999; 10525</t>
         </is>
       </c>
     </row>
@@ -1302,17 +1302,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1900; 10009</t>
+          <t>1904; 9970</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 3656</t>
+          <t>0; 3395</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2180; 12271</t>
+          <t>2514; 11168</t>
         </is>
       </c>
     </row>
@@ -1375,17 +1375,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 1546</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 2830</t>
+          <t>0; 2708</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 3491</t>
+          <t>0; 3197</t>
         </is>
       </c>
     </row>
@@ -1448,17 +1448,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 4845</t>
+          <t>0; 4373</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 2182</t>
+          <t>0; 2197</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>525; 5016</t>
+          <t>550; 5216</t>
         </is>
       </c>
     </row>
@@ -1521,7 +1521,7 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>0; 1056</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -1531,7 +1531,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0; 2856</t>
+          <t>0; 2973</t>
         </is>
       </c>
     </row>
@@ -1594,17 +1594,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>18488; 41401</t>
+          <t>17661; 40750</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>4589; 18495</t>
+          <t>4325; 18671</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>25652; 50338</t>
+          <t>26403; 51410</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P32E$calle_2023-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P32E$calle_2023-Edad-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>46,98%</t>
+          <t>40,15%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>40,66%</t>
+          <t>34,19%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>44,61%</t>
+          <t>37,9%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>21,27; 76,76</t>
+          <t>16,4; 69,37</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>12,85; 74,23</t>
+          <t>9,12; 68,18</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>26,44; 66,47</t>
+          <t>19,68; 60,18</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>14,45%</t>
+          <t>12,86%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>9,08%</t>
+          <t>8,47%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>12,46%</t>
+          <t>11,26%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,81; 36,69</t>
+          <t>3,36; 34,61</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 54,45</t>
+          <t>0,0; 41,74</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3,52; 31,49</t>
+          <t>2,76; 24,46</t>
         </is>
       </c>
     </row>
@@ -649,7 +649,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>19,83%</t>
+          <t>19,41%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -659,7 +659,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>16,48%</t>
+          <t>15,88%</t>
         </is>
       </c>
     </row>
@@ -672,7 +672,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>7,43; 39,5</t>
+          <t>7,4; 39,92</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -682,7 +682,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6,19; 32,58</t>
+          <t>5,94; 32,44</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>18,04%</t>
+          <t>17,36%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>15,36%</t>
+          <t>14,46%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>6,9; 36,14</t>
+          <t>6,39; 34,55</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 37,57</t>
+          <t>0,0; 32,7</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6,86; 30,49</t>
+          <t>5,69; 28,2</t>
         </is>
       </c>
     </row>
@@ -754,12 +754,12 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>10,46%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,34%</t>
         </is>
       </c>
     </row>
@@ -777,12 +777,12 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 44,28</t>
+          <t>0,0; 41,16</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,09</t>
+          <t>0,0; 12,25</t>
         </is>
       </c>
     </row>
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>11,37%</t>
+          <t>11,51%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>15,6%</t>
+          <t>15,92%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>12,44%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 33,01</t>
+          <t>0,0; 35,62</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 63,17</t>
+          <t>0,0; 52,22</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3,29; 31,18</t>
+          <t>3,32; 34,07</t>
         </is>
       </c>
     </row>
@@ -854,12 +854,12 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>31,67%</t>
+          <t>25,77%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>7,17%</t>
         </is>
       </c>
     </row>
@@ -882,7 +882,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 43,54</t>
+          <t>0,0; 32,2</t>
         </is>
       </c>
     </row>
@@ -899,17 +899,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>18,86%</t>
+          <t>17,45%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>17,99%</t>
+          <t>15,72%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>18,62%</t>
+          <t>16,96%</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>12,26; 28,28</t>
+          <t>11,7; 25,85</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>7,9; 34,12</t>
+          <t>7,73; 28,38</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>13,28; 25,86</t>
+          <t>12,23; 23,78</t>
         </is>
       </c>
     </row>
@@ -1060,17 +1060,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>12047</t>
+          <t>11867</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>6242</t>
+          <t>6141</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>18289</t>
+          <t>18008</t>
         </is>
       </c>
     </row>
@@ -1083,17 +1083,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>5455; 19683</t>
+          <t>4848; 20501</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1973; 11396</t>
+          <t>1638; 12246</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>10838; 27251</t>
+          <t>9353; 28595</t>
         </is>
       </c>
     </row>
@@ -1133,17 +1133,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>3318</t>
+          <t>3592</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1229</t>
+          <t>1353</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>4547</t>
+          <t>4945</t>
         </is>
       </c>
     </row>
@@ -1156,17 +1156,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>876; 8426</t>
+          <t>940; 9663</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 7373</t>
+          <t>0; 6666</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1286; 11494</t>
+          <t>1211; 10736</t>
         </is>
       </c>
     </row>
@@ -1206,7 +1206,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>5325</t>
+          <t>5760</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -1216,7 +1216,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5325</t>
+          <t>5761</t>
         </is>
       </c>
     </row>
@@ -1229,7 +1229,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1995; 10609</t>
+          <t>2198; 11849</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1999; 10525</t>
+          <t>2154; 11766</t>
         </is>
       </c>
     </row>
@@ -1279,17 +1279,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>4976</t>
+          <t>5289</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>651</t>
+          <t>671</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>5626</t>
+          <t>5960</t>
         </is>
       </c>
     </row>
@@ -1302,17 +1302,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1904; 9970</t>
+          <t>1948; 10527</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 3395</t>
+          <t>0; 3511</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2514; 11168</t>
+          <t>2346; 11622</t>
         </is>
       </c>
     </row>
@@ -1357,12 +1357,12 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>627</t>
+          <t>702</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>627</t>
+          <t>702</t>
         </is>
       </c>
     </row>
@@ -1380,12 +1380,12 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 2708</t>
+          <t>0; 2762</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 3197</t>
+          <t>0; 3669</t>
         </is>
       </c>
     </row>
@@ -1425,17 +1425,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>1506</t>
+          <t>1666</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>542</t>
+          <t>613</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2048</t>
+          <t>2278</t>
         </is>
       </c>
     </row>
@@ -1448,17 +1448,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 4373</t>
+          <t>0; 5155</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 2197</t>
+          <t>0; 2010</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>550; 5216</t>
+          <t>608; 6241</t>
         </is>
       </c>
     </row>
@@ -1503,12 +1503,12 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>550</t>
+          <t>610</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>550</t>
+          <t>610</t>
         </is>
       </c>
     </row>
@@ -1526,12 +1526,12 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>0; 1738</t>
+          <t>0; 2368</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0; 2973</t>
+          <t>0; 2741</t>
         </is>
       </c>
     </row>
@@ -1571,17 +1571,17 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>27172</t>
+          <t>28174</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>9842</t>
+          <t>10090</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>37014</t>
+          <t>38264</t>
         </is>
       </c>
     </row>
@@ -1594,17 +1594,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>17661; 40750</t>
+          <t>18895; 41745</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>4325; 18671</t>
+          <t>4961; 18216</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>26403; 51410</t>
+          <t>27593; 53671</t>
         </is>
       </c>
     </row>
